--- a/reports/tables/first_visit_sensitivity_target_top1_vs_top2.xlsx
+++ b/reports/tables/first_visit_sensitivity_target_top1_vs_top2.xlsx
@@ -489,32 +489,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CatBoost_Baseline_NoResampling</t>
+          <t>LightGBM_ADASYN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.006961746780136199</v>
+        <v>0.01968846638997852</v>
       </c>
       <c r="D2" t="n">
         <v>0.852112676056338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3123300090661831</v>
+        <v>0.3327289211242067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07387057387057387</v>
+        <v>0.07595731324544884</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9704225352112676</v>
+        <v>0.9721854304635762</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3023850085178876</v>
+        <v>0.3215502555366269</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6505576979556396</v>
+        <v>0.6562527932782551</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1491494729928106</v>
+        <v>0.154830500217629</v>
       </c>
     </row>
     <row r="3">
@@ -523,32 +523,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling</t>
+          <t>CatBoost_Baseline_NoResampling</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2063818457332277</v>
+        <v>0.4054959217357728</v>
       </c>
       <c r="D3" t="n">
         <v>0.852112676056338</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3662737987307343</v>
+        <v>0.4329102447869447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07965766951942067</v>
+        <v>0.08819241982507289</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9746682750301568</v>
+        <v>0.9784836065573771</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3530664395229983</v>
+        <v>0.4156729131175468</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6629853919528048</v>
+        <v>0.6946164749147652</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1472147220993271</v>
+        <v>0.1494584991534506</v>
       </c>
     </row>
     <row r="4">
@@ -557,32 +557,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CatBoost_Baseline_NoResampling</t>
+          <t>LightGBM_ADASYN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.003701885700134357</v>
+        <v>0.009818277240934065</v>
       </c>
       <c r="D4" t="n">
         <v>0.9014084507042254</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2230281051677244</v>
+        <v>0.21441523118767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06948968512486428</v>
+        <v>0.06878022568511553</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9723320158102767</v>
+        <v>0.971252566735113</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2155025553662692</v>
+        <v>0.2074105621805792</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6505576979556396</v>
+        <v>0.6562527932782551</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1491494729928106</v>
+        <v>0.154830500217629</v>
       </c>
     </row>
     <row r="5">
@@ -591,32 +591,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling</t>
+          <t>CatBoost_Baseline_NoResampling</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.109806584810605</v>
+        <v>0.3312940759735054</v>
       </c>
       <c r="D5" t="n">
         <v>0.9014084507042254</v>
       </c>
       <c r="E5" t="n">
-        <v>0.171804170444243</v>
+        <v>0.270625566636446</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06547314578005115</v>
+        <v>0.0736902705814623</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9643765903307888</v>
+        <v>0.9770867430441899</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1673764906303237</v>
+        <v>0.260221465076661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6629853919528048</v>
+        <v>0.6946164749147652</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1472147220993271</v>
+        <v>0.1494584991534506</v>
       </c>
     </row>
     <row r="6">
@@ -625,32 +625,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CatBoost_Baseline_NoResampling</t>
+          <t>LightGBM_ADASYN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.001700089658810787</v>
+        <v>0.004971107961559266</v>
       </c>
       <c r="D6" t="n">
         <v>0.9507042253521126</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1409791477787851</v>
+        <v>0.1201269265639166</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06650246305418719</v>
+        <v>0.06502890173410404</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9779874213836478</v>
+        <v>0.9742647058823529</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1354344122657581</v>
+        <v>0.1158432708688245</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6505576979556396</v>
+        <v>0.6562527932782551</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1491494729928106</v>
+        <v>0.154830500217629</v>
       </c>
     </row>
     <row r="7">
@@ -659,32 +659,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling</t>
+          <t>CatBoost_Baseline_NoResampling</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.07963687715281877</v>
+        <v>0.2766773947498319</v>
       </c>
       <c r="D7" t="n">
         <v>0.9507042253521126</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08658204895738894</v>
+        <v>0.1731640979147779</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06279069767441861</v>
+        <v>0.06891271056661562</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9646464646464646</v>
+        <v>0.9820051413881749</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08432708688245315</v>
+        <v>0.1656729131175468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6629853919528048</v>
+        <v>0.6946164749147652</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1472147220993271</v>
+        <v>0.1494584991534506</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +719,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Point_Difference_CatBoost_Baseline_NoResampling_minus_LightGBM_Baseline_NoResampling</t>
+          <t>Point_Difference_LightGBM_ADASYN_minus_CatBoost_Baseline_NoResampling</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0001547293801025679</v>
+        <v>0.0001370751920560835</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01527011156782152</v>
+        <v>-0.01493685419058547</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01429089026915119</v>
+        <v>0.01460394701270622</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -786,16 +786,16 @@
         <v>1000</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05394378966455121</v>
+        <v>-0.100181323662738</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05530124411490717</v>
+        <v>-0.08895261744544503</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1666024087177572</v>
+        <v>-0.2114456462173293</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1121164487048367</v>
+        <v>0.0327786321064966</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -816,16 +816,16 @@
         <v>1000</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.005787095648846802</v>
+        <v>-0.01223510657962405</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.006601161436770986</v>
+        <v>-0.0109269827051246</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01910721810587489</v>
+        <v>-0.02376305365035665</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008957916989757432</v>
+        <v>0.002902544691430311</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -846,16 +846,16 @@
         <v>1000</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.004245739818889205</v>
+        <v>-0.0062981760938009</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.003391703330976993</v>
+        <v>-0.005891719555056879</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01213004612307744</v>
+        <v>-0.01828058770003308</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01960847608892146</v>
+        <v>0.003333052678175409</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -876,16 +876,16 @@
         <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05068143100511074</v>
+        <v>-0.09412265758091992</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.05194783478637514</v>
+        <v>-0.08356337982397935</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1564794112252385</v>
+        <v>-0.1987187385205643</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1057796488391448</v>
+        <v>0.03112961068118364</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -909,13 +909,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000301222923712769</v>
+        <v>-7.563844191072833e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.01450080515297902</v>
+        <v>-0.01481481481481484</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01493391819528316</v>
+        <v>0.01504626951995372</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -936,16 +936,16 @@
         <v>1000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05122393472348141</v>
+        <v>-0.05621033544877604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01870814070334394</v>
+        <v>-0.04786528079210578</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.124099111175454</v>
+        <v>-0.2105560459531382</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1480193523885009</v>
+        <v>0.0923235273320679</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -966,16 +966,16 @@
         <v>1000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004016539344813136</v>
+        <v>-0.004910044896346763</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001066817307839419</v>
+        <v>-0.005177203218746099</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01335712362536436</v>
+        <v>-0.02354731627493356</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01219638356797296</v>
+        <v>0.008172437666987524</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         <v>1000</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00795542547948791</v>
+        <v>-0.005834176309076899</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005378743347247764</v>
+        <v>-0.003142981198749525</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01114573201357324</v>
+        <v>-0.01485346331668022</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02666247659930714</v>
+        <v>0.009894323971606112</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1026,16 +1026,16 @@
         <v>1000</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0481260647359455</v>
+        <v>-0.05281090289608179</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01754821259977987</v>
+        <v>-0.04496563547405276</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.117003318422557</v>
+        <v>-0.1977077827723407</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1390371588597111</v>
+        <v>0.08723073612009059</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0001573176073929714</v>
+        <v>0.0003485059548730222</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.01449539828625828</v>
+        <v>-0.01449275362318836</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01428571428571424</v>
+        <v>0.01503759398496241</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1086,16 +1086,16 @@
         <v>1000</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05439709882139618</v>
+        <v>-0.05303717135086129</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06045532023479568</v>
+        <v>-0.02316800335187575</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.01264900638872582</v>
+        <v>-0.1048421532408962</v>
       </c>
       <c r="G13" t="n">
-        <v>0.135189414739324</v>
+        <v>0.05455941529112258</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1116,16 +1116,16 @@
         <v>1000</v>
       </c>
       <c r="D14" t="n">
-        <v>0.003711765379768583</v>
+        <v>-0.003883808832511576</v>
       </c>
       <c r="E14" t="n">
-        <v>0.004262390263059665</v>
+        <v>-0.001659490411064146</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.000897983175007654</v>
+        <v>-0.007698179311243288</v>
       </c>
       <c r="G14" t="n">
-        <v>0.009862351801018994</v>
+        <v>0.003930384146383507</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
         <v>1000</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01334095673718316</v>
+        <v>-0.00774043550582193</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01363116422182232</v>
+        <v>-0.003501272895744742</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.002402549055095937</v>
+        <v>-0.01927822498027836</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03660689601002638</v>
+        <v>0.007974059794410989</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
         <v>1000</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05110732538330494</v>
+        <v>-0.0498296422487223</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05679472054134715</v>
+        <v>-0.02178290285275343</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01188261445296902</v>
+        <v>-0.09869729958675322</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1283116629326814</v>
+        <v>0.05142365147719393</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CatBoost_Baseline_NoResampling</t>
+          <t>LightGBM_ADASYN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.006961746780136199</v>
+        <v>0.01968846638997852</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006684397249985532</v>
+        <v>0.01989853136872996</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003701885700134357</v>
+        <v>0.009773819641193117</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008987665117849798</v>
+        <v>0.02757430107353143</v>
       </c>
     </row>
     <row r="3">
@@ -1267,20 +1267,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling</t>
+          <t>CatBoost_Baseline_NoResampling</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2063818457332277</v>
+        <v>0.4054959217357728</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2086006817643291</v>
+        <v>0.3985511514483335</v>
       </c>
       <c r="E3" t="n">
-        <v>0.109806584810605</v>
+        <v>0.3091367581914767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2680494740295289</v>
+        <v>0.4326626510166267</v>
       </c>
     </row>
     <row r="4">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CatBoost_Baseline_NoResampling</t>
+          <t>LightGBM_ADASYN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.003701885700134357</v>
+        <v>0.009818277240934065</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004192607254263107</v>
+        <v>0.01135610104713148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002419185600072203</v>
+        <v>0.006116923565077743</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00698096178555095</v>
+        <v>0.02250879702582794</v>
       </c>
     </row>
     <row r="5">
@@ -1311,20 +1311,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling</t>
+          <t>CatBoost_Baseline_NoResampling</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.109806584810605</v>
+        <v>0.3312940759735054</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1334147151792882</v>
+        <v>0.332859764986704</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08634188489852061</v>
+        <v>0.2769657186589747</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2321703176443541</v>
+        <v>0.4054959217357728</v>
       </c>
     </row>
     <row r="6">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CatBoost_Baseline_NoResampling</t>
+          <t>LightGBM_ADASYN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.001700089658810787</v>
+        <v>0.004971107961559266</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002009593938493527</v>
+        <v>0.005764277911125612</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001118949251500219</v>
+        <v>0.002898505688812394</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003518179943029679</v>
+        <v>0.009773819641193117</v>
       </c>
     </row>
     <row r="7">
@@ -1355,20 +1355,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling</t>
+          <t>CatBoost_Baseline_NoResampling</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.07963687715281877</v>
+        <v>0.2766773947498319</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08290116565985949</v>
+        <v>0.2707852223681879</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07168652230384953</v>
+        <v>0.2383515377132093</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1093837784395525</v>
+        <v>0.3091367581914767</v>
       </c>
     </row>
   </sheetData>
@@ -1393,27 +1393,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling_higher_specificity</t>
+          <t>CatBoost_Baseline_NoResampling_higher_specificity</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling_higher_PPV</t>
+          <t>CatBoost_Baseline_NoResampling_higher_PPV</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling_NPV_not_lower</t>
+          <t>CatBoost_Baseline_NoResampling_NPV_not_lower</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling_higher_low_probability_rate</t>
+          <t>CatBoost_Baseline_NoResampling_higher_low_probability_rate</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>LightGBM_Baseline_NoResampling_preferred_on_all_clinical_point_estimates</t>
+          <t>CatBoost_Baseline_NoResampling_preferred_on_all_clinical_point_estimates</t>
         </is>
       </c>
     </row>
@@ -1442,19 +1442,19 @@
         <v>0.9</v>
       </c>
       <c r="B3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1462,19 +1462,19 @@
         <v>0.95</v>
       </c>
       <c r="B4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
